--- a/tools/excel/gdpr/gdpr-checklist.xlsx
+++ b/tools/excel/gdpr/gdpr-checklist.xlsx
@@ -947,7 +947,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Virksomheter med minst 250 ansatte, eller som utfører behandling som sannsynligvis vil medføre en risiko for de registrerte, som ikke skjer leilighetsvis eller som omfatter særlige kategorier av personopplysninger, må føre en oppdatert og detaljert protokoll over behandlingsaktivitetene sine (art. 30) og gjøre den tilgjengelig for tilsynsmyndigheten på anmodning. Den beste måten å dokumentere etterlevelse av GDPR på er en vurdering av personvernkonsekvenser (art. 35).
+          <t>Virksomheter med minst 250 ansatte, eller som utfører behandling som sannsynligvis vil medføre en risiko for de registrertes rettigheter og friheter, som ikke skjer leilighetsvis, eller som omfatter særlige kategorier av personopplysninger eller personopplysninger om straffedommer og lovovertredelser, må føre en oppdatert og detaljert protokoll over behandlingsaktivitetene sine (art. 30) og gjøre den tilgjengelig for tilsynsmyndigheten på anmodning. Den beste måten å dokumentere etterlevelse av GDPR på er en vurdering av personvernkonsekvenser (art. 35).
 Virksomheter med færre enn 250 ansatte bør også gjøre en slik kartlegging, fordi den gjør det lettere å oppfylle de andre kravene i GDPR. Oversikten bør inneholde: formålene med behandlingen, hvilke opplysninger dere behandler, hvem i virksomheten som har tilgang til dem, eventuelle tredjeparter som har tilgang (og hvor de holder til), hva dere gjør for å beskytte opplysningene (f.eks. kryptering), og når dere planlegger å slette dem (hvis mulig).</t>
         </is>
       </c>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Ved brudd på personopplysningssikkerheten må dere uten ugrunnet opphold, og om mulig senest 72 timer etter at dere fikk kjennskap til bruddet, melde det til tilsynsmyndigheten der dere hører hjemme (art. 33 nr. 1), med mindre bruddet sannsynligvis ikke vil medføre en risiko for de registrerte. En oversikt over tilsynsmyndighetene i mange av EUs medlemsstater finnes her. GDPR sier ikke hvem dere skal melde til hvis virksomheten ikke er etablert i EU. For virksomheter i engelskspråklige land utenfor EU kan det være enklest å melde til det irske datatilsynet (Data Protection Commission). Dere må også uten ugrunnet opphold underrette de registrerte om bruddet dersom det er sannsynlig at det vil medføre en høy risiko for dem (art. 34). Underretning er for eksempel ikke påkrevd hvis de stjålne opplysningene er kryptert.</t>
+          <t>Ved brudd på personopplysningssikkerheten må dere uten ugrunnet opphold, og om mulig senest 72 timer etter at dere fikk kjennskap til bruddet, melde det til tilsynsmyndigheten der dere hører hjemme (art. 33 nr. 1), med mindre bruddet sannsynligvis ikke vil medføre en risiko for fysiske personers rettigheter og friheter. En oversikt over tilsynsmyndighetene i mange av EUs medlemsstater finnes her. GDPR sier ikke hvem dere skal melde til hvis virksomheten ikke er etablert i EU. For virksomheter i engelskspråklige land utenfor EU kan det være enklest å melde til det irske datatilsynet (Data Protection Commission). Dere må også uten ugrunnet opphold underrette de registrerte om bruddet dersom det er sannsynlig at det vil medføre en høy risiko for dem (art. 34). Underretning er for eksempel ikke påkrevd hvis de stjålne opplysningene er kryptert.</t>
         </is>
       </c>
     </row>

--- a/tools/excel/gdpr/gdpr-checklist.xlsx
+++ b/tools/excel/gdpr/gdpr-checklist.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="library_meta" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="checklist_meta" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="checklist_content" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="library_meta" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="checklist_meta" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="checklist_content" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -614,6 +614,30 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>name[nb]</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>GDPR-sjekkliste for behandlingsansvarlige</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>description[nb]</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>GDPR.EU-sjekkliste for behandlingsansvarlige (https://gdpr.eu/checklist/)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -625,7 +649,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -745,6 +769,30 @@
       <c r="B10" t="inlineStr">
         <is>
           <t>Liste de contrôle RGPD pour les responsables du traitement des données  (https://gdpr.eu/checklist/)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>name[nb]</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>GDPR-sjekkliste for behandlingsansvarlige</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>description[nb]</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>GDPR.EU-sjekkliste for behandlingsansvarlige (https://gdpr.eu/checklist/)</t>
         </is>
       </c>
     </row>
@@ -759,7 +807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="47.6640625" customWidth="1" min="4" max="4"/>
@@ -815,6 +863,16 @@
           <t>description[fr]</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>name[nb]</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>description[nb]</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="17" customHeight="1">
       <c r="B2" t="n">
@@ -835,6 +893,11 @@
           <t>Base légale et transparence</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Behandlingsgrunnlag og åpenhet</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="289" customHeight="1">
       <c r="A3" t="inlineStr">
@@ -877,6 +940,17 @@
 Les organisations de moins de 250 employés devraient également effectuer une évaluation, car cela facilitera la conformité aux autres exigences du RGPD. Dans votre liste, vous devez inclure : les finalités du traitement, le type de données que vous traitez, qui y a accès dans votre organisation, les tiers (et où ils se trouvent) qui y ont accès, ce que vous faites pour protéger les données (par exemple, le cryptage) et quand vous prévoyez de les effacer (si possible).</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Kartlegg hvilke opplysninger dere behandler, og hvem som har tilgang til dem.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Virksomheter med minst 250 ansatte, eller som utfører behandling som sannsynligvis vil medføre en risiko for de registrerte, som ikke skjer leilighetsvis eller som omfatter særlige kategorier av personopplysninger, må føre en oppdatert og detaljert protokoll over behandlingsaktivitetene sine (art. 30) og gjøre den tilgjengelig for tilsynsmyndigheten på anmodning. Den beste måten å dokumentere etterlevelse av GDPR på er en vurdering av personvernkonsekvenser (art. 35).
+Virksomheter med færre enn 250 ansatte bør også gjøre en slik kartlegging, fordi den gjør det lettere å oppfylle de andre kravene i GDPR. Oversikten bør inneholde: formålene med behandlingen, hvilke opplysninger dere behandler, hvem i virksomheten som har tilgang til dem, eventuelle tredjeparter som har tilgang (og hvor de holder til), hva dere gjør for å beskytte opplysningene (f.eks. kryptering), og når dere planlegger å slette dem (hvis mulig).</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="255" customHeight="1">
       <c r="A4" t="inlineStr">
@@ -917,6 +991,16 @@
           <t>Le traitement des données est illégal au regard du RGPD à moins que vous ne puissiez le justifier selon l’une des six conditions énumérées à l’article 6. Les articles 7 à 11 contiennent d’autres dispositions relatives aux enfants et à des catégories particulières de données à caractère personnel. Examinez ces dispositions, choisissez une base légale pour le traitement et documentez votre justification. Notez que si vous choisissez le « consentement » comme base légale, il existe des obligations supplémentaires, notamment la possibilité de révoquer leur consentement en permanence. Si vous vous fondez sur la légalité des « intérêts légitimes », vous devez être en mesure de démontrer que vous avez effectué une évaluation des facteurs relatifs à la vie privée.</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Ha et rettslig grunnlag for behandlingsaktivitetene.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Behandling av personopplysninger er ulovlig etter GDPR med mindre den har grunnlag i ett av de seks vilkårene i art. 6 nr. 1. Art. 7–11 har flere bestemmelser om barn og særlige kategorier av personopplysninger. Gå gjennom disse bestemmelsene, velg et behandlingsgrunnlag og dokumenter begrunnelsen. Merk at samtykke som behandlingsgrunnlag gir ekstra plikter, blant annet at de registrerte til enhver tid skal kunne trekke samtykket tilbake. Bruker dere «berettigede interesser» som behandlingsgrunnlag, må dere kunne vise at dere har gjort en interesseavveining (art. 6 nr. 1 bokstav f).</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="187" customHeight="1">
       <c r="A5" t="inlineStr">
@@ -955,6 +1039,16 @@
       <c r="I5" s="1" t="inlineStr">
         <is>
           <t>Vous devez dire aux gens que vous collectez leurs données et pourquoi (article 12). Vous devez expliquer comment les données sont traitées, qui y a accès et comment vous les protégez. Ces informations doivent être incluses dans votre politique de confidentialité et fournies aux personnes concernées au moment où vous collectez leurs données. Il doit être présenté « sous une forme concise, transparente, intelligible et facilement accessible, dans un langage clair et simple, notamment pour toute information s’adressant spécifiquement à un enfant ».</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Gi tydelig informasjon om behandlingen og behandlingsgrunnlaget i personvernerklæringen.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Dere må fortelle folk at dere samler inn opplysninger om dem, og hvorfor (art. 12–14). Forklar hvordan opplysningene behandles, hvem som har tilgang til dem, og hvordan dere sikrer dem. Denne informasjonen bør stå i personvernerklæringen og gis til de registrerte når opplysningene samles inn. Den skal gis «på en kortfattet, åpen, forståelig og lett tilgjengelig måte og på et klart og enkelt språk, især når det gjelder informasjon som spesifikt er rettet mot et barn» (art. 12 nr. 1).</t>
         </is>
       </c>
     </row>
@@ -977,6 +1071,11 @@
           <t>Sécurité des données</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Informasjonssikkerhet</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="272" customHeight="1">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1116,16 @@
           <t>Vous devez suivre les principes de « protection des données dès la conception et par défaut », y compris la mise en œuvre de « mesures techniques et organisationnelles appropriées » pour protéger les données. En d’autres termes, la protection des données est quelque chose que vous devez désormais prendre en compte chaque fois que vous faites quoi que ce soit avec les données personnelles d’autres personnes. Vous devez également vous assurer que tout traitement de données à caractère personnel respecte les principes de protection des données décrits à l’article 5. Les mesures techniques comprennent le cryptage, et les mesures organisationnelles consistent à limiter la quantité de données personnelles que vous collectez ou à supprimer les données dont vous n’avez plus besoin. Le fait est que vous et vos employés devez en être toujours conscients.</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Ta hensyn til personvern hele tiden, fra dere begynner å utvikle et produkt til hver gang dere behandler opplysninger.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Dere må følge prinsippene om «innebygd personvern og personvern som standardinnstilling», blant annet ved å gjennomføre «egnede tekniske og organisatoriske tiltak» for å beskytte opplysningene. Personvern er med andre ord noe dere må tenke på hver gang dere gjør noe med andres personopplysninger. Dere må også sørge for at all behandling av personopplysninger følger prinsippene i art. 5. Tekniske tiltak er for eksempel kryptering, og organisatoriske tiltak er for eksempel å begrense hvor mye personopplysninger dere samler inn, eller å slette opplysninger dere ikke lenger trenger. Poenget er at dette er noe dere og de ansatte alltid må være bevisste på.</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="119" customHeight="1">
       <c r="A8" t="inlineStr">
@@ -1057,6 +1166,16 @@
           <t>La plupart des outils de productivité utilisés par les entreprises sont désormais disponibles avec un chiffrement de bout en bout intégré, notamment les e-mails, la messagerie, les notes et le stockage dans le cloud. Le RGPD exige que les organisations utilisent le cryptage ou la pseudeonymisation chaque fois que cela est possible.</t>
         </is>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Krypter, pseudonymiser eller anonymiser personopplysninger der det er mulig.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>De fleste produktivitetsverktøyene virksomheter bruker, finnes nå med innebygd ende-til-ende-kryptering, blant annet e-post, meldingstjenester, notater og skylagring. GDPR nevner pseudonymisering og kryptering som eksempler på egnede tiltak (art. 32 nr. 1 bokstav a), og virksomheter bør bruke dem der det er hensiktsmessig.</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="187" customHeight="1">
       <c r="A9" t="inlineStr">
@@ -1097,6 +1216,16 @@
           <t>Même si votre sécurité technique est forte, la sécurité opérationnelle peut toujours être un maillon faible. Créez une politique de sécurité qui garantit que les membres de votre équipe sont bien informés sur la sécurité des données. Il doit inclure des conseils sur la sécurité des e-mails, les mots de passe, l’authentification à deux facteurs, le cryptage des appareils et les VPN. Les employés qui ont accès aux données personnelles et les employés non techniques doivent recevoir une formation supplémentaire sur les exigences du RGPD.</t>
         </is>
       </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Lag en intern sikkerhetspolicy for de ansatte, og øk bevisstheten om personvern.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Selv om den tekniske sikkerheten er god, kan den operative sikkerheten være et svakt ledd. Lag en sikkerhetspolicy som sørger for at de ansatte har kunnskap om informasjonssikkerhet. Den bør gi veiledning om e-postsikkerhet, passord, tofaktorautentisering, kryptering av enheter og VPN. Ansatte som har tilgang til personopplysninger, og ansatte uten teknisk bakgrunn, bør få ekstra opplæring i kravene i GDPR.</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="255" customHeight="1">
       <c r="A10" t="inlineStr">
@@ -1137,6 +1266,16 @@
           <t>Une analyse d’impact sur la protection des données (également appelée évaluation de l’impact sur la vie privée) est un moyen de vous aider à comprendre comment votre produit ou service pourrait mettre en péril les données de vos clients, ainsi que comment minimiser ces risques. L’Information Commissioner’s Office (ICO) du Royaume-Uni a publié une liste de contrôle d’évaluation de l’impact sur la protection des données sur son site Web. Le RGPD exige que les organisations effectuent ce type d’analyse chaque fois qu’elles prévoient d’utiliser les données des personnes de manière à ce qu’il soit « susceptible d’entraîner un risque élevé pour [leurs] droits et libertés ». L’ICO recommande de le faire à tout moment lorsque vous êtes sur le point de traiter des données personnelles.</t>
         </is>
       </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Vit når dere skal gjennomføre en vurdering av personvernkonsekvenser, og ha en prosess for å gjennomføre den.</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>En vurdering av personvernkonsekvenser (DPIA) hjelper dere å forstå hvordan produktet eller tjenesten deres kan sette kundenes opplysninger i fare, og hvordan dere kan redusere den risikoen. Det britiske datatilsynet (ICO) har en sjekkliste for DPIA på nettsidene sine. GDPR krever at virksomheter gjør en slik analyse når de planlegger å bruke personopplysninger på en måte der det er sannsynlig at det «vil medføre en høy risiko for fysiske personers rettigheter og friheter». ICO anbefaler å gjøre det hver gang dere skal behandle personopplysninger.</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="255" customHeight="1">
       <c r="A11" t="inlineStr">
@@ -1175,6 +1314,16 @@
       <c r="I11" s="1" t="inlineStr">
         <is>
           <t>En cas de violation de données et d’exposition de données personnelles, vous devez en informer l’autorité de contrôle de votre juridiction dans les 72 heures. Une liste de nombreuses autorités de surveillance des États membres de l’UE peut être consultée ici. Le RGPD ne précise pas qui vous devez notifier si vous n’êtes pas une organisation basée dans l’UE. Pour ceux qui se trouvent dans des pays anglophones non membres de l’UE, il peut être plus facile d’en informer le Bureau du commissaire à la protection des données en Irlande. Vous êtes également tenu de communiquer rapidement les violations de données à vos personnes concernées, sauf si la violation n’est pas susceptible de les mettre en danger (par exemple, si les données volées sont cryptées).</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Ha en prosess for å melde fra til tilsynsmyndigheten og underrette de registrerte ved brudd på personopplysningssikkerheten.</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Ved brudd på personopplysningssikkerheten må dere uten ugrunnet opphold, og om mulig senest 72 timer etter at dere fikk kjennskap til bruddet, melde det til tilsynsmyndigheten der dere hører hjemme (art. 33 nr. 1), med mindre bruddet sannsynligvis ikke vil medføre en risiko for de registrerte. En oversikt over tilsynsmyndighetene i mange av EUs medlemsstater finnes her. GDPR sier ikke hvem dere skal melde til hvis virksomheten ikke er etablert i EU. For virksomheter i engelskspråklige land utenfor EU kan det være enklest å melde til det irske datatilsynet (Data Protection Commission). Dere må også uten ugrunnet opphold underrette de registrerte om bruddet dersom det er sannsynlig at det vil medføre en høy risiko for dem (art. 34). Underretning er for eksempel ikke påkrevd hvis de stjålne opplysningene er kryptert.</t>
         </is>
       </c>
     </row>
@@ -1197,6 +1346,11 @@
           <t>Responsabilisation et gouvernance</t>
         </is>
       </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Ansvar og styring</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="119" customHeight="1">
       <c r="A13" t="inlineStr">
@@ -1237,6 +1391,16 @@
           <t>Une autre partie de la « protection des données dès la conception et par défaut » (article 25) consiste à s’assurer qu’une personne de votre organisation est responsable de la conformité au RGPD. Cette personne devrait être habilitée à évaluer les politiques de protection des données et la mise en œuvre de ces politiques.</t>
         </is>
       </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Utpek en som har ansvaret for at hele virksomheten etterlever GDPR.</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>En annen del av «innebygd personvern og personvern som standardinnstilling» (art. 25) er å sørge for at noen i virksomheten har ansvaret for etterlevelsen av GDPR. Denne personen bør ha myndighet til å vurdere personvernpolicyer og hvordan de gjennomføres.</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="187" customHeight="1">
       <c r="A14" t="inlineStr">
@@ -1277,6 +1441,16 @@
           <t>Cela inclut tous les services tiers qui traitent les données personnelles de vos personnes concernées, y compris les logiciels analytiques, les services de messagerie, les serveurs cloud, etc. La grande majorité des services ont un accord standard de traitement des données disponible sur leurs sites Web pour que vous puissiez les consulter. Ils énoncent les droits et obligations de chaque partie en matière de conformité au RGPD. Vous ne devez faire appel qu’à des tiers fiables et capables d’apporter des garanties suffisantes en matière de protection des données.</t>
         </is>
       </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Inngå en databehandleravtale med alle databehandlere som behandler personopplysninger på vegne av virksomheten.</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Dette gjelder alle leverandører som behandler personopplysninger om de registrerte på vegne av dere (databehandlere), blant annet analyseverktøy, e-posttjenester og skytjenester. De aller fleste tjenester har en standard databehandleravtale på nettsidene sine som dere kan gå gjennom. Den fastsetter rettighetene og pliktene til hver part for å etterleve GDPR. Bruk bare databehandlere som er pålitelige og gir tilstrekkelige garantier for personvernet (art. 28 nr. 1).</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="204" customHeight="1">
       <c r="A15" t="inlineStr">
@@ -1317,6 +1491,16 @@
           <t>Si vous traitez des données relatives à des personnes dans un État membre particulier, vous devez désigner un représentant dans ce pays qui peut communiquer en votre nom avec les autorités de protection des données. Le RGPD et ses documents officiels ne donnent pas d’indications pour les situations où le traitement affecte des personnes de l’UE dans plusieurs États membres. Jusqu’à ce que cette exigence soit interprétée, il peut être prudent de désigner un représentant dans un État membre qui utilise votre langue. Certaines organisations, comme les organismes publics, ne sont pas tenues de désigner un représentant dans l’UE.</t>
         </is>
       </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Hvis virksomheten er etablert utenfor EU/EØS, utpek en representant i en av medlemsstatene.</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Behandler dere opplysninger om personer i én bestemt medlemsstat, må dere utpeke en representant i det landet som kan kommunisere med tilsynsmyndighetene på deres vegne. Berører behandlingen personer i flere medlemsstater, skal representanten være etablert i en av medlemsstatene der de registrerte befinner seg (art. 27 nr. 3); det kan være lurt å velge en medlemsstat som bruker deres språk. Enkelte virksomheter, for eksempel offentlige organer, trenger ikke å utpeke en representant i EU/EØS (art. 27 nr. 2).</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="187" customHeight="1">
       <c r="A16" t="inlineStr">
@@ -1355,6 +1539,16 @@
       <c r="I16" s="1" t="inlineStr">
         <is>
           <t>Il existe trois circonstances dans lesquelles les organisations sont tenues d’avoir un délégué à la protection des données (DPO), mais ce n’est pas une mauvaise idée d’en avoir un même si la règle ne s’applique pas à vous. Le DPD doit être un expert en matière de protection des données dont le travail consiste à surveiller la conformité au RGPD, à évaluer les risques liés à la protection des données, à donner des conseils sur les analyses d’impact relatives à la protection des données et à coopérer avec les régulateurs.</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Utpek et personvernombud (hvis nødvendig)</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Virksomheter må ha et personvernombud i tre tilfeller, men det kan være lurt å ha et selv om regelen ikke gjelder for dere. Personvernombudet bør være ekspert på personvern og har som oppgave å overvåke etterlevelsen av GDPR, vurdere personvernrisiko, gi råd om vurderinger av personvernkonsekvenser og samarbeide med tilsynsmyndigheten.</t>
         </is>
       </c>
     </row>
@@ -1377,6 +1571,11 @@
           <t>Droits à la vie privée</t>
         </is>
       </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>De registrertes rettigheter</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="187" customHeight="1">
       <c r="A18" t="inlineStr">
@@ -1417,6 +1616,16 @@
           <t>Les gens ont le droit de voir quelles données personnelles vous détenez à leur sujet (article 15) et comment vous les utilisez. Ils ont également le droit de savoir combien de temps vous prévoyez de conserver leurs informations et la raison pour laquelle elles sont conservées pendant cette période. Vous devez leur envoyer la première copie de ces informations gratuitement, mais vous pouvez facturer des frais raisonnables pour les copies suivantes. Assurez-vous de pouvoir vérifier l’identité de la personne qui demande les données. Vous devriez être en mesure de donner suite à ces demandes dans un délai d’un mois.</t>
         </is>
       </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Kundene kan enkelt be om og få alle opplysningene dere har om dem.</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Folk har rett til innsyn i hvilke personopplysninger dere har om dem (art. 15), og i hvordan dere bruker dem. De har også rett til å vite hvor lenge dere planlegger å lagre opplysningene, og hvorfor. Den første kopien skal være gratis, men dere kan ta et rimelig gebyr for flere kopier. Sørg for at dere kan bekrefte identiteten til den som ber om opplysningene. Dere må svare på slike forespørsler uten ugrunnet opphold og senest innen én måned (art. 12 nr. 3).</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="153" customHeight="1">
       <c r="A19" t="inlineStr">
@@ -1457,6 +1666,16 @@
           <t>Faites de votre mieux pour maintenir les données à jour en mettant en place un processus de qualité des données, et faites en sorte qu’il soit facile pour vos clients de consulter (Article 15) et de mettre à jour leurs informations personnelles pour en assurer l’exactitude et l’exhaustivité. Assurez-vous de pouvoir vérifier l’identité de la personne qui demande les données. Vous devriez être en mesure de donner suite aux demandes au titre de l’article 16 dans un délai d’un mois.</t>
         </is>
       </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Kundene kan enkelt rette eller oppdatere uriktige eller ufullstendige opplysninger.</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Gjør det dere kan for å holde opplysningene oppdatert ved å ha en prosess for datakvalitet, og gjør det enkelt for kundene å se (art. 15) og oppdatere personopplysningene sine slik at de er korrekte og fullstendige. Sørg for at dere kan bekrefte identiteten til den som ber om opplysningene. Dere må svare på forespørsler etter art. 16 uten ugrunnet opphold og senest innen én måned (art. 12 nr. 3).</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="136" customHeight="1">
       <c r="A20" t="inlineStr">
@@ -1497,6 +1716,16 @@
           <t>Les gens ont généralement le droit de vous demander de supprimer toutes les données personnelles que vous avez à leur sujet, et vous devez honorer leur demande dans un délai d’environ un mois. Il y a cinq motifs pour lesquels vous pouvez refuser la demande, tels que l’exercice de la liberté d’expression ou le respect d’une obligation légale. Vous devez également tenter de vérifier l’identité de la personne qui fait la demande.</t>
         </is>
       </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Kundene kan enkelt be om å få personopplysningene sine slettet.</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Folk har som hovedregel rett til å be dere slette alle personopplysningene dere har om dem, og dere må etterkomme forespørselen uten ugrunnet opphold og senest innen én måned (art. 12 nr. 3). Det finnes fem grunner til å avslå forespørselen (art. 17 nr. 3), for eksempel utøvelse av ytrings- og informasjonsfriheten eller oppfyllelse av en rettslig forpliktelse. Dere må også forsøke å bekrefte identiteten til den som ber om slettingen.</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="170" customHeight="1">
       <c r="A21" t="inlineStr">
@@ -1537,6 +1766,16 @@
           <t>Vos personnes concernées peuvent demander à restreindre ou à arrêter le traitement de leurs données (article 18) si certains motifs s’appliquent, principalement en cas de litige quant à la licéité du traitement ou à l’exactitude des données. Vous êtes tenu d’honorer leur demande dans un délai d’environ un mois. Bien que le traitement soit limité, vous êtes toujours autorisé à continuer à stocker leurs données. Vous devez informer la personne concernée avant de recommencer à traiter ses données.</t>
         </is>
       </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Kundene kan enkelt be dere stanse behandlingen av opplysningene deres.</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>De registrerte kan kreve at behandlingen av opplysningene deres begrenses (art. 18) når visse vilkår er oppfylt, hovedsakelig når de bestrider at behandlingen er lovlig eller at opplysningene er riktige. Dere må etterkomme forespørselen uten ugrunnet opphold og senest innen én måned (art. 12 nr. 3). Mens behandlingen er begrenset, kan dere fortsatt lagre opplysningene. Dere må underrette den registrerte før begrensningen av behandlingen oppheves.</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="153" customHeight="1">
       <c r="A22" t="inlineStr">
@@ -1577,6 +1816,16 @@
           <t>Cela signifie que vous devez être en mesure d’envoyer leurs données personnelles (article 20) dans un format lisible par tous (par exemple une feuille de calcul) soit à eux, soit à un tiers qu’ils désignent. Cela peut sembler injuste d’un point de vue commercial, dans la mesure où vous devrez peut-être remettre les données de vos clients à un concurrent. Mais du point de vue de la protection de la vie privée, l’idée est que ce sont les gens qui sont propriétaires de leurs données, pas vous.</t>
         </is>
       </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Kundene kan enkelt få en kopi av personopplysningene sine i et format som lett kan overføres til en annen virksomhet.</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Det betyr at dere skal kunne utlevere personopplysningene deres (art. 20) i et strukturert, alminnelig anvendt og maskinlesbart format (f.eks. et regneark), enten til dem selv eller, når det er teknisk mulig, direkte til en annen behandlingsansvarlig de utpeker. Fra et forretningsperspektiv kan det virke urimelig at dere kanskje må gi kundenes opplysninger til en konkurrent. Men fra et personvernperspektiv er tanken at det er folk selv som eier opplysningene sine, ikke dere.</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="85" customHeight="1">
       <c r="A23" t="inlineStr">
@@ -1617,6 +1866,16 @@
           <t>Si vous traitez leurs données à des fins de marketing direct, vous devez cesser immédiatement de les traiter (article 21) à cette fin. Sinon, vous pourrez peut-être contester leur objection si vous pouvez démontrer l’existence de « motifs légitimes impérieux ».</t>
         </is>
       </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Kundene kan enkelt protestere mot at dere behandler opplysningene deres.</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Behandler dere opplysningene deres for direkte markedsføring, må dere straks stanse behandlingen for det formålet (art. 21). Ellers kan dere avvise protesten hvis dere kan påvise «tvingende berettigede grunner».</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="187" customHeight="1">
       <c r="A24" t="inlineStr">
@@ -1655,6 +1914,16 @@
       <c r="I24" s="1" t="inlineStr">
         <is>
           <t>Certains types d’organisations utilisent des processus automatisés (article 22) pour les aider à prendre des décisions concernant des personnes qui ont des effets juridiques ou « d’importance similaire ». Si vous pensez que cela s’applique à vous, vous devrez mettre en place une procédure pour vous assurer que vous protégez leurs droits, libertés et intérêts légitimes. Vous devez permettre aux gens de demander facilement une intervention humaine, de peser sur les décisions et de remettre en question les décisions que vous avez déjà prises.</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Tar dere avgjørelser om personer basert på automatiserte prosesser, har dere en prosedyre for å ivareta rettighetene deres.</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Noen typer virksomheter bruker automatiserte prosesser (art. 22) til å ta avgjørelser om personer som har rettsvirkning for dem eller «på tilsvarende måte i betydelig grad påvirker» dem. Gjelder det dere, må dere ha en prosedyre som ivaretar rettighetene, frihetene og de berettigede interessene deres. Det må være enkelt for folk å be om menneskelig inngripen, å uttale seg om avgjørelser og å bestride avgjørelser som allerede er tatt.</t>
         </is>
       </c>
     </row>

--- a/tools/excel/gdpr/gdpr-checklist.xlsx
+++ b/tools/excel/gdpr/gdpr-checklist.xlsx
@@ -1323,7 +1323,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Ved brudd på personopplysningssikkerheten må dere uten ugrunnet opphold, og om mulig senest 72 timer etter at dere fikk kjennskap til bruddet, melde det til tilsynsmyndigheten der dere hører hjemme (art. 33 nr. 1), med mindre bruddet sannsynligvis ikke vil medføre en risiko for fysiske personers rettigheter og friheter. En oversikt over tilsynsmyndighetene i mange av EUs medlemsstater finnes her. GDPR sier ikke hvem dere skal melde til hvis virksomheten ikke er etablert i EU. For virksomheter i engelskspråklige land utenfor EU kan det være enklest å melde til det irske datatilsynet (Data Protection Commission). Dere må også uten ugrunnet opphold underrette de registrerte om bruddet dersom det er sannsynlig at det vil medføre en høy risiko for dem (art. 34). Underretning er for eksempel ikke påkrevd hvis de stjålne opplysningene er kryptert.</t>
+          <t>Ved brudd på personopplysningssikkerheten må dere uten ugrunnet opphold, og om mulig senest 72 timer etter at dere fikk kjennskap til bruddet, melde det til tilsynsmyndigheten der dere hører hjemme (art. 33 nr. 1), med mindre bruddet sannsynligvis ikke vil medføre en risiko for fysiske personers rettigheter og friheter. En oversikt over tilsynsmyndighetene i mange av EUs medlemsstater finnes her. GDPR sier ikke hvem dere skal melde til hvis virksomheten ikke er etablert i EU. For virksomheter i engelskspråklige land utenfor EU kan det være enklest å melde til det irske datatilsynet (Data Protection Commission). Dere må også uten ugrunnet opphold underrette de registrerte om bruddet dersom det er sannsynlig at det vil medføre en høy risiko for dem (art. 34). Underretning er ikke påkrevd hvis opplysningene er gjort uleselige for alle som ikke har autorisert tilgang til dem, for eksempel ved kryptering (art. 34 nr. 3 bokstav a).</t>
         </is>
       </c>
     </row>

--- a/tools/excel/gdpr/gdpr-checklist.xlsx
+++ b/tools/excel/gdpr/gdpr-checklist.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="library_meta" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="checklist_meta" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="checklist_content" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="library_meta" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="checklist_meta" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="checklist_content" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -614,6 +614,30 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>name[nb]</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>GDPR-sjekkliste for behandlingsansvarlige</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>description[nb]</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>GDPR.EU-sjekkliste for behandlingsansvarlige (https://gdpr.eu/checklist/)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -625,7 +649,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -745,6 +769,30 @@
       <c r="B10" t="inlineStr">
         <is>
           <t>Liste de contrôle RGPD pour les responsables du traitement des données  (https://gdpr.eu/checklist/)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>name[nb]</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>GDPR-sjekkliste for behandlingsansvarlige</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>description[nb]</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>GDPR.EU-sjekkliste for behandlingsansvarlige (https://gdpr.eu/checklist/)</t>
         </is>
       </c>
     </row>
@@ -759,7 +807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="47.6640625" customWidth="1" min="4" max="4"/>
@@ -815,6 +863,16 @@
           <t>description[fr]</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>name[nb]</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>description[nb]</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="17" customHeight="1">
       <c r="B2" t="n">
@@ -835,6 +893,11 @@
           <t>Base légale et transparence</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Behandlingsgrunnlag og åpenhet</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="289" customHeight="1">
       <c r="A3" t="inlineStr">
@@ -877,6 +940,17 @@
 Les organisations de moins de 250 employés devraient également effectuer une évaluation, car cela facilitera la conformité aux autres exigences du RGPD. Dans votre liste, vous devez inclure : les finalités du traitement, le type de données que vous traitez, qui y a accès dans votre organisation, les tiers (et où ils se trouvent) qui y ont accès, ce que vous faites pour protéger les données (par exemple, le cryptage) et quand vous prévoyez de les effacer (si possible).</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Kartlegg hvilke opplysninger dere behandler, og hvem som har tilgang til dem.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Virksomheter med minst 250 ansatte, eller som utfører behandling som sannsynligvis vil medføre en risiko for de registrertes rettigheter og friheter, som ikke skjer leilighetsvis, eller som omfatter særlige kategorier av personopplysninger eller personopplysninger om straffedommer og lovovertredelser, må føre en oppdatert og detaljert protokoll over behandlingsaktivitetene sine (art. 30) og gjøre den tilgjengelig for tilsynsmyndigheten på anmodning. Den beste måten å dokumentere etterlevelse av GDPR på er en vurdering av personvernkonsekvenser (art. 35).
+Virksomheter med færre enn 250 ansatte bør også gjøre en slik kartlegging, fordi den gjør det lettere å oppfylle de andre kravene i GDPR. Oversikten bør inneholde: formålene med behandlingen, hvilke opplysninger dere behandler, hvem i virksomheten som har tilgang til dem, eventuelle tredjeparter som har tilgang (og hvor de holder til), hva dere gjør for å beskytte opplysningene (f.eks. kryptering), og når dere planlegger å slette dem (hvis mulig).</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="255" customHeight="1">
       <c r="A4" t="inlineStr">
@@ -917,6 +991,16 @@
           <t>Le traitement des données est illégal au regard du RGPD à moins que vous ne puissiez le justifier selon l’une des six conditions énumérées à l’article 6. Les articles 7 à 11 contiennent d’autres dispositions relatives aux enfants et à des catégories particulières de données à caractère personnel. Examinez ces dispositions, choisissez une base légale pour le traitement et documentez votre justification. Notez que si vous choisissez le « consentement » comme base légale, il existe des obligations supplémentaires, notamment la possibilité de révoquer leur consentement en permanence. Si vous vous fondez sur la légalité des « intérêts légitimes », vous devez être en mesure de démontrer que vous avez effectué une évaluation des facteurs relatifs à la vie privée.</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Ha et rettslig grunnlag for behandlingsaktivitetene.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Behandling av personopplysninger er ulovlig etter GDPR med mindre den har grunnlag i ett av de seks vilkårene i art. 6 nr. 1. Art. 7–11 har flere bestemmelser om barn og særlige kategorier av personopplysninger. Gå gjennom disse bestemmelsene, velg et behandlingsgrunnlag og dokumenter begrunnelsen. Merk at samtykke som behandlingsgrunnlag gir ekstra plikter, blant annet at de registrerte til enhver tid skal kunne trekke samtykket tilbake. Bruker dere «berettigede interesser» som behandlingsgrunnlag, må dere kunne vise at dere har gjort en interesseavveining (art. 6 nr. 1 bokstav f).</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="187" customHeight="1">
       <c r="A5" t="inlineStr">
@@ -955,6 +1039,16 @@
       <c r="I5" s="1" t="inlineStr">
         <is>
           <t>Vous devez dire aux gens que vous collectez leurs données et pourquoi (article 12). Vous devez expliquer comment les données sont traitées, qui y a accès et comment vous les protégez. Ces informations doivent être incluses dans votre politique de confidentialité et fournies aux personnes concernées au moment où vous collectez leurs données. Il doit être présenté « sous une forme concise, transparente, intelligible et facilement accessible, dans un langage clair et simple, notamment pour toute information s’adressant spécifiquement à un enfant ».</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Gi tydelig informasjon om behandlingen og behandlingsgrunnlaget i personvernerklæringen.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Dere må fortelle folk at dere samler inn opplysninger om dem, og hvorfor (art. 12–14). Forklar hvordan opplysningene behandles, hvem som har tilgang til dem, og hvordan dere sikrer dem. Denne informasjonen bør stå i personvernerklæringen og gis til de registrerte når opplysningene samles inn. Den skal gis «på en kortfattet, åpen, forståelig og lett tilgjengelig måte og på et klart og enkelt språk, især når det gjelder informasjon som spesifikt er rettet mot et barn» (art. 12 nr. 1).</t>
         </is>
       </c>
     </row>
@@ -977,6 +1071,11 @@
           <t>Sécurité des données</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Informasjonssikkerhet</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="272" customHeight="1">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1116,16 @@
           <t>Vous devez suivre les principes de « protection des données dès la conception et par défaut », y compris la mise en œuvre de « mesures techniques et organisationnelles appropriées » pour protéger les données. En d’autres termes, la protection des données est quelque chose que vous devez désormais prendre en compte chaque fois que vous faites quoi que ce soit avec les données personnelles d’autres personnes. Vous devez également vous assurer que tout traitement de données à caractère personnel respecte les principes de protection des données décrits à l’article 5. Les mesures techniques comprennent le cryptage, et les mesures organisationnelles consistent à limiter la quantité de données personnelles que vous collectez ou à supprimer les données dont vous n’avez plus besoin. Le fait est que vous et vos employés devez en être toujours conscients.</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Ta hensyn til personvern hele tiden, fra dere begynner å utvikle et produkt til hver gang dere behandler opplysninger.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Dere må følge prinsippene om «innebygd personvern og personvern som standardinnstilling», blant annet ved å gjennomføre «egnede tekniske og organisatoriske tiltak» for å beskytte opplysningene. Personvern er med andre ord noe dere må tenke på hver gang dere gjør noe med andres personopplysninger. Dere må også sørge for at all behandling av personopplysninger følger prinsippene i art. 5. Tekniske tiltak er for eksempel kryptering, og organisatoriske tiltak er for eksempel å begrense hvor mye personopplysninger dere samler inn, eller å slette opplysninger dere ikke lenger trenger. Poenget er at dette er noe dere og de ansatte alltid må være bevisste på.</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="119" customHeight="1">
       <c r="A8" t="inlineStr">
@@ -1057,6 +1166,16 @@
           <t>La plupart des outils de productivité utilisés par les entreprises sont désormais disponibles avec un chiffrement de bout en bout intégré, notamment les e-mails, la messagerie, les notes et le stockage dans le cloud. Le RGPD exige que les organisations utilisent le cryptage ou la pseudeonymisation chaque fois que cela est possible.</t>
         </is>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Krypter, pseudonymiser eller anonymiser personopplysninger der det er mulig.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>De fleste produktivitetsverktøyene virksomheter bruker, finnes nå med innebygd ende-til-ende-kryptering, blant annet e-post, meldingstjenester, notater og skylagring. GDPR nevner pseudonymisering og kryptering som eksempler på egnede tiltak (art. 32 nr. 1 bokstav a), og virksomheter bør bruke dem der det er hensiktsmessig.</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="187" customHeight="1">
       <c r="A9" t="inlineStr">
@@ -1097,6 +1216,16 @@
           <t>Même si votre sécurité technique est forte, la sécurité opérationnelle peut toujours être un maillon faible. Créez une politique de sécurité qui garantit que les membres de votre équipe sont bien informés sur la sécurité des données. Il doit inclure des conseils sur la sécurité des e-mails, les mots de passe, l’authentification à deux facteurs, le cryptage des appareils et les VPN. Les employés qui ont accès aux données personnelles et les employés non techniques doivent recevoir une formation supplémentaire sur les exigences du RGPD.</t>
         </is>
       </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Lag en intern sikkerhetspolicy for de ansatte, og øk bevisstheten om personvern.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Selv om den tekniske sikkerheten er god, kan den operative sikkerheten være et svakt ledd. Lag en sikkerhetspolicy som sørger for at de ansatte har kunnskap om informasjonssikkerhet. Den bør gi veiledning om e-postsikkerhet, passord, tofaktorautentisering, kryptering av enheter og VPN. Ansatte som har tilgang til personopplysninger, og ansatte uten teknisk bakgrunn, bør få ekstra opplæring i kravene i GDPR.</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="255" customHeight="1">
       <c r="A10" t="inlineStr">
@@ -1137,6 +1266,16 @@
           <t>Une analyse d’impact sur la protection des données (également appelée évaluation de l’impact sur la vie privée) est un moyen de vous aider à comprendre comment votre produit ou service pourrait mettre en péril les données de vos clients, ainsi que comment minimiser ces risques. L’Information Commissioner’s Office (ICO) du Royaume-Uni a publié une liste de contrôle d’évaluation de l’impact sur la protection des données sur son site Web. Le RGPD exige que les organisations effectuent ce type d’analyse chaque fois qu’elles prévoient d’utiliser les données des personnes de manière à ce qu’il soit « susceptible d’entraîner un risque élevé pour [leurs] droits et libertés ». L’ICO recommande de le faire à tout moment lorsque vous êtes sur le point de traiter des données personnelles.</t>
         </is>
       </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Vit når dere skal gjennomføre en vurdering av personvernkonsekvenser, og ha en prosess for å gjennomføre den.</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>En vurdering av personvernkonsekvenser (DPIA) hjelper dere å forstå hvordan produktet eller tjenesten deres kan sette kundenes opplysninger i fare, og hvordan dere kan redusere den risikoen. Det britiske datatilsynet (ICO) har en sjekkliste for DPIA på nettsidene sine. GDPR krever at virksomheter gjør en slik analyse når de planlegger å bruke personopplysninger på en måte der det er sannsynlig at det «vil medføre en høy risiko for fysiske personers rettigheter og friheter». ICO anbefaler å gjøre det hver gang dere skal behandle personopplysninger.</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="255" customHeight="1">
       <c r="A11" t="inlineStr">
@@ -1175,6 +1314,16 @@
       <c r="I11" s="1" t="inlineStr">
         <is>
           <t>En cas de violation de données et d’exposition de données personnelles, vous devez en informer l’autorité de contrôle de votre juridiction dans les 72 heures. Une liste de nombreuses autorités de surveillance des États membres de l’UE peut être consultée ici. Le RGPD ne précise pas qui vous devez notifier si vous n’êtes pas une organisation basée dans l’UE. Pour ceux qui se trouvent dans des pays anglophones non membres de l’UE, il peut être plus facile d’en informer le Bureau du commissaire à la protection des données en Irlande. Vous êtes également tenu de communiquer rapidement les violations de données à vos personnes concernées, sauf si la violation n’est pas susceptible de les mettre en danger (par exemple, si les données volées sont cryptées).</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Ha en prosess for å melde fra til tilsynsmyndigheten og underrette de registrerte ved brudd på personopplysningssikkerheten.</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Ved brudd på personopplysningssikkerheten må dere uten ugrunnet opphold, og om mulig senest 72 timer etter at dere fikk kjennskap til bruddet, melde det til tilsynsmyndigheten der dere hører hjemme (art. 33 nr. 1), med mindre bruddet sannsynligvis ikke vil medføre en risiko for fysiske personers rettigheter og friheter. En oversikt over tilsynsmyndighetene i mange av EUs medlemsstater finnes her. GDPR sier ikke hvem dere skal melde til hvis virksomheten ikke er etablert i EU. For virksomheter i engelskspråklige land utenfor EU kan det være enklest å melde til det irske datatilsynet (Data Protection Commission). Dere må også uten ugrunnet opphold underrette de registrerte om bruddet dersom det er sannsynlig at det vil medføre en høy risiko for dem (art. 34). Underretning er ikke påkrevd hvis opplysningene er gjort uleselige for alle som ikke har autorisert tilgang til dem, for eksempel ved kryptering (art. 34 nr. 3 bokstav a).</t>
         </is>
       </c>
     </row>
@@ -1197,6 +1346,11 @@
           <t>Responsabilisation et gouvernance</t>
         </is>
       </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Ansvar og styring</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="119" customHeight="1">
       <c r="A13" t="inlineStr">
@@ -1237,6 +1391,16 @@
           <t>Une autre partie de la « protection des données dès la conception et par défaut » (article 25) consiste à s’assurer qu’une personne de votre organisation est responsable de la conformité au RGPD. Cette personne devrait être habilitée à évaluer les politiques de protection des données et la mise en œuvre de ces politiques.</t>
         </is>
       </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Utpek en som har ansvaret for at hele virksomheten etterlever GDPR.</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>En annen del av «innebygd personvern og personvern som standardinnstilling» (art. 25) er å sørge for at noen i virksomheten har ansvaret for etterlevelsen av GDPR. Denne personen bør ha myndighet til å vurdere personvernpolicyer og hvordan de gjennomføres.</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="187" customHeight="1">
       <c r="A14" t="inlineStr">
@@ -1277,6 +1441,16 @@
           <t>Cela inclut tous les services tiers qui traitent les données personnelles de vos personnes concernées, y compris les logiciels analytiques, les services de messagerie, les serveurs cloud, etc. La grande majorité des services ont un accord standard de traitement des données disponible sur leurs sites Web pour que vous puissiez les consulter. Ils énoncent les droits et obligations de chaque partie en matière de conformité au RGPD. Vous ne devez faire appel qu’à des tiers fiables et capables d’apporter des garanties suffisantes en matière de protection des données.</t>
         </is>
       </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Inngå en databehandleravtale med alle databehandlere som behandler personopplysninger på vegne av virksomheten.</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Dette gjelder alle leverandører som behandler personopplysninger om de registrerte på vegne av dere (databehandlere), blant annet analyseverktøy, e-posttjenester og skytjenester. De aller fleste tjenester har en standard databehandleravtale på nettsidene sine som dere kan gå gjennom. Den fastsetter rettighetene og pliktene til hver part for å etterleve GDPR. Bruk bare databehandlere som er pålitelige og gir tilstrekkelige garantier for personvernet (art. 28 nr. 1).</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="204" customHeight="1">
       <c r="A15" t="inlineStr">
@@ -1317,6 +1491,16 @@
           <t>Si vous traitez des données relatives à des personnes dans un État membre particulier, vous devez désigner un représentant dans ce pays qui peut communiquer en votre nom avec les autorités de protection des données. Le RGPD et ses documents officiels ne donnent pas d’indications pour les situations où le traitement affecte des personnes de l’UE dans plusieurs États membres. Jusqu’à ce que cette exigence soit interprétée, il peut être prudent de désigner un représentant dans un État membre qui utilise votre langue. Certaines organisations, comme les organismes publics, ne sont pas tenues de désigner un représentant dans l’UE.</t>
         </is>
       </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Hvis virksomheten er etablert utenfor EU/EØS, utpek en representant i en av medlemsstatene.</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Behandler dere opplysninger om personer i én bestemt medlemsstat, må dere utpeke en representant i det landet som kan kommunisere med tilsynsmyndighetene på deres vegne. Berører behandlingen personer i flere medlemsstater, skal representanten være etablert i en av medlemsstatene der de registrerte befinner seg (art. 27 nr. 3); det kan være lurt å velge en medlemsstat som bruker deres språk. Enkelte virksomheter, for eksempel offentlige organer, trenger ikke å utpeke en representant i EU/EØS (art. 27 nr. 2).</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="187" customHeight="1">
       <c r="A16" t="inlineStr">
@@ -1355,6 +1539,16 @@
       <c r="I16" s="1" t="inlineStr">
         <is>
           <t>Il existe trois circonstances dans lesquelles les organisations sont tenues d’avoir un délégué à la protection des données (DPO), mais ce n’est pas une mauvaise idée d’en avoir un même si la règle ne s’applique pas à vous. Le DPD doit être un expert en matière de protection des données dont le travail consiste à surveiller la conformité au RGPD, à évaluer les risques liés à la protection des données, à donner des conseils sur les analyses d’impact relatives à la protection des données et à coopérer avec les régulateurs.</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Utpek et personvernombud (hvis nødvendig)</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Virksomheter må ha et personvernombud i tre tilfeller, men det kan være lurt å ha et selv om regelen ikke gjelder for dere. Personvernombudet bør være ekspert på personvern og har som oppgave å overvåke etterlevelsen av GDPR, vurdere personvernrisiko, gi råd om vurderinger av personvernkonsekvenser og samarbeide med tilsynsmyndigheten.</t>
         </is>
       </c>
     </row>
@@ -1377,6 +1571,11 @@
           <t>Droits à la vie privée</t>
         </is>
       </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>De registrertes rettigheter</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="187" customHeight="1">
       <c r="A18" t="inlineStr">
@@ -1417,6 +1616,16 @@
           <t>Les gens ont le droit de voir quelles données personnelles vous détenez à leur sujet (article 15) et comment vous les utilisez. Ils ont également le droit de savoir combien de temps vous prévoyez de conserver leurs informations et la raison pour laquelle elles sont conservées pendant cette période. Vous devez leur envoyer la première copie de ces informations gratuitement, mais vous pouvez facturer des frais raisonnables pour les copies suivantes. Assurez-vous de pouvoir vérifier l’identité de la personne qui demande les données. Vous devriez être en mesure de donner suite à ces demandes dans un délai d’un mois.</t>
         </is>
       </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Kundene kan enkelt be om og få alle opplysningene dere har om dem.</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Folk har rett til innsyn i hvilke personopplysninger dere har om dem (art. 15), og i hvordan dere bruker dem. De har også rett til å vite hvor lenge dere planlegger å lagre opplysningene, og hvorfor. Den første kopien skal være gratis, men dere kan ta et rimelig gebyr for flere kopier. Sørg for at dere kan bekrefte identiteten til den som ber om opplysningene. Dere må svare på slike forespørsler uten ugrunnet opphold og senest innen én måned (art. 12 nr. 3).</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="153" customHeight="1">
       <c r="A19" t="inlineStr">
@@ -1457,6 +1666,16 @@
           <t>Faites de votre mieux pour maintenir les données à jour en mettant en place un processus de qualité des données, et faites en sorte qu’il soit facile pour vos clients de consulter (Article 15) et de mettre à jour leurs informations personnelles pour en assurer l’exactitude et l’exhaustivité. Assurez-vous de pouvoir vérifier l’identité de la personne qui demande les données. Vous devriez être en mesure de donner suite aux demandes au titre de l’article 16 dans un délai d’un mois.</t>
         </is>
       </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Kundene kan enkelt rette eller oppdatere uriktige eller ufullstendige opplysninger.</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Gjør det dere kan for å holde opplysningene oppdatert ved å ha en prosess for datakvalitet, og gjør det enkelt for kundene å se (art. 15) og oppdatere personopplysningene sine slik at de er korrekte og fullstendige. Sørg for at dere kan bekrefte identiteten til den som ber om opplysningene. Dere må svare på forespørsler etter art. 16 uten ugrunnet opphold og senest innen én måned (art. 12 nr. 3).</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="136" customHeight="1">
       <c r="A20" t="inlineStr">
@@ -1497,6 +1716,16 @@
           <t>Les gens ont généralement le droit de vous demander de supprimer toutes les données personnelles que vous avez à leur sujet, et vous devez honorer leur demande dans un délai d’environ un mois. Il y a cinq motifs pour lesquels vous pouvez refuser la demande, tels que l’exercice de la liberté d’expression ou le respect d’une obligation légale. Vous devez également tenter de vérifier l’identité de la personne qui fait la demande.</t>
         </is>
       </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Kundene kan enkelt be om å få personopplysningene sine slettet.</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Folk har som hovedregel rett til å be dere slette alle personopplysningene dere har om dem, og dere må etterkomme forespørselen uten ugrunnet opphold og senest innen én måned (art. 12 nr. 3). Det finnes fem grunner til å avslå forespørselen (art. 17 nr. 3), for eksempel utøvelse av ytrings- og informasjonsfriheten eller oppfyllelse av en rettslig forpliktelse. Dere må også forsøke å bekrefte identiteten til den som ber om slettingen.</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="170" customHeight="1">
       <c r="A21" t="inlineStr">
@@ -1537,6 +1766,16 @@
           <t>Vos personnes concernées peuvent demander à restreindre ou à arrêter le traitement de leurs données (article 18) si certains motifs s’appliquent, principalement en cas de litige quant à la licéité du traitement ou à l’exactitude des données. Vous êtes tenu d’honorer leur demande dans un délai d’environ un mois. Bien que le traitement soit limité, vous êtes toujours autorisé à continuer à stocker leurs données. Vous devez informer la personne concernée avant de recommencer à traiter ses données.</t>
         </is>
       </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Kundene kan enkelt be dere stanse behandlingen av opplysningene deres.</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>De registrerte kan kreve at behandlingen av opplysningene deres begrenses (art. 18) når visse vilkår er oppfylt, hovedsakelig når de bestrider at behandlingen er lovlig eller at opplysningene er riktige. Dere må etterkomme forespørselen uten ugrunnet opphold og senest innen én måned (art. 12 nr. 3). Mens behandlingen er begrenset, kan dere fortsatt lagre opplysningene. Dere må underrette den registrerte før begrensningen av behandlingen oppheves.</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="153" customHeight="1">
       <c r="A22" t="inlineStr">
@@ -1577,6 +1816,16 @@
           <t>Cela signifie que vous devez être en mesure d’envoyer leurs données personnelles (article 20) dans un format lisible par tous (par exemple une feuille de calcul) soit à eux, soit à un tiers qu’ils désignent. Cela peut sembler injuste d’un point de vue commercial, dans la mesure où vous devrez peut-être remettre les données de vos clients à un concurrent. Mais du point de vue de la protection de la vie privée, l’idée est que ce sont les gens qui sont propriétaires de leurs données, pas vous.</t>
         </is>
       </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Kundene kan enkelt få en kopi av personopplysningene sine i et format som lett kan overføres til en annen virksomhet.</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Det betyr at dere skal kunne utlevere personopplysningene deres (art. 20) i et strukturert, alminnelig anvendt og maskinlesbart format (f.eks. et regneark), enten til dem selv eller, når det er teknisk mulig, direkte til en annen behandlingsansvarlig de utpeker. Fra et forretningsperspektiv kan det virke urimelig at dere kanskje må gi kundenes opplysninger til en konkurrent. Men fra et personvernperspektiv er tanken at det er folk selv som eier opplysningene sine, ikke dere.</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="85" customHeight="1">
       <c r="A23" t="inlineStr">
@@ -1617,6 +1866,16 @@
           <t>Si vous traitez leurs données à des fins de marketing direct, vous devez cesser immédiatement de les traiter (article 21) à cette fin. Sinon, vous pourrez peut-être contester leur objection si vous pouvez démontrer l’existence de « motifs légitimes impérieux ».</t>
         </is>
       </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Kundene kan enkelt protestere mot at dere behandler opplysningene deres.</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Behandler dere opplysningene deres for direkte markedsføring, må dere straks stanse behandlingen for det formålet (art. 21). Ellers kan dere avvise protesten hvis dere kan påvise «tvingende berettigede grunner».</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="187" customHeight="1">
       <c r="A24" t="inlineStr">
@@ -1655,6 +1914,16 @@
       <c r="I24" s="1" t="inlineStr">
         <is>
           <t>Certains types d’organisations utilisent des processus automatisés (article 22) pour les aider à prendre des décisions concernant des personnes qui ont des effets juridiques ou « d’importance similaire ». Si vous pensez que cela s’applique à vous, vous devrez mettre en place une procédure pour vous assurer que vous protégez leurs droits, libertés et intérêts légitimes. Vous devez permettre aux gens de demander facilement une intervention humaine, de peser sur les décisions et de remettre en question les décisions que vous avez déjà prises.</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Tar dere avgjørelser om personer basert på automatiserte prosesser, har dere en prosedyre for å ivareta rettighetene deres.</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Noen typer virksomheter bruker automatiserte prosesser (art. 22) til å ta avgjørelser om personer som har rettsvirkning for dem eller «på tilsvarende måte i betydelig grad påvirker» dem. Gjelder det dere, må dere ha en prosedyre som ivaretar rettighetene, frihetene og de berettigede interessene deres. Det må være enkelt for folk å be om menneskelig inngripen, å uttale seg om avgjørelser og å bestride avgjørelser som allerede er tatt.</t>
         </is>
       </c>
     </row>
